--- a/data/MK_YFINANCE_DATA_20260623.xlsx
+++ b/data/MK_YFINANCE_DATA_20260623.xlsx
@@ -22597,10 +22597,10 @@
         </is>
       </c>
       <c r="F419" t="n">
-        <v>8928.950000000001</v>
+        <v>8942.5</v>
       </c>
       <c r="G419" t="n">
-        <v>8928.950000000001</v>
+        <v>8942.5</v>
       </c>
       <c r="H419" t="n">
         <v>9083.540000000001</v>
@@ -22609,19 +22609,19 @@
         <v>9175.450000000001</v>
       </c>
       <c r="J419" t="n">
-        <v>8928.950000000001</v>
+        <v>8911.799999999999</v>
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>82.23K</t>
+          <t>98.99K</t>
         </is>
       </c>
       <c r="L419" t="n">
-        <v>-0.0136</v>
+        <v>-0.0121</v>
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(12,'20260623',8928.95,8928.95,9083.54,9175.45,8928.95,'82.23K',-0.0136,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(12,'20260623',8942.5,8942.5,9083.54,9175.45,8911.8,'98.99K',-0.0121,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -24344,10 +24344,10 @@
         </is>
       </c>
       <c r="F452" t="n">
-        <v>1443.2</v>
+        <v>1447.88</v>
       </c>
       <c r="G452" t="n">
-        <v>1443.2</v>
+        <v>1447.88</v>
       </c>
       <c r="H452" t="n">
         <v>1470.75</v>
@@ -24356,19 +24356,19 @@
         <v>1487.31</v>
       </c>
       <c r="J452" t="n">
-        <v>1443.14</v>
+        <v>1439.81</v>
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>32.12K</t>
+          <t>39.34K</t>
         </is>
       </c>
       <c r="L452" t="n">
-        <v>-0.0112</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(13,'20260623',1443.2,1443.2,1470.75,1487.31,1443.14,'32.12K',-0.0112,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(13,'20260623',1447.88,1447.88,1470.75,1487.31,1439.81,'39.34K',-0.0079,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -26091,10 +26091,10 @@
         </is>
       </c>
       <c r="F485" t="n">
-        <v>938.58</v>
+        <v>937.1799999999999</v>
       </c>
       <c r="G485" t="n">
-        <v>938.58</v>
+        <v>937.1799999999999</v>
       </c>
       <c r="H485" t="n">
         <v>958.64</v>
@@ -26103,19 +26103,19 @@
         <v>971.6900000000001</v>
       </c>
       <c r="J485" t="n">
-        <v>938.58</v>
+        <v>935.67</v>
       </c>
       <c r="K485" t="inlineStr">
         <is>
-          <t>128.96K</t>
+          <t>160.17K</t>
         </is>
       </c>
       <c r="L485" t="n">
-        <v>-0.029</v>
+        <v>-0.0304</v>
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(14,'20260623',938.58,938.58,958.64,971.69,938.58,'128.96K',-0.029,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(14,'20260623',937.18,937.18,958.64,971.69,935.67,'160.17K',-0.0304,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -35087,10 +35087,10 @@
         </is>
       </c>
       <c r="F663" t="n">
-        <v>1539.48</v>
+        <v>1538.89</v>
       </c>
       <c r="G663" t="n">
-        <v>1539.48</v>
+        <v>1538.89</v>
       </c>
       <c r="H663" t="n">
         <v>1533.38</v>
@@ -35103,11 +35103,11 @@
       </c>
       <c r="K663" t="inlineStr"/>
       <c r="L663" t="n">
-        <v>0.0053</v>
+        <v>0.0049</v>
       </c>
       <c r="M663" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(19,'20260623',1539.48,1539.48,1533.38,1541.78,1533.01,NULL,0.0053,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(19,'20260623',1538.89,1538.89,1533.38,1541.78,1533.01,NULL,0.0049,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -36994,10 +36994,10 @@
         </is>
       </c>
       <c r="F702" t="n">
-        <v>9.506</v>
+        <v>9.5</v>
       </c>
       <c r="G702" t="n">
-        <v>9.506</v>
+        <v>9.5</v>
       </c>
       <c r="H702" t="n">
         <v>9.468999999999999</v>
@@ -37010,11 +37010,11 @@
       </c>
       <c r="K702" t="inlineStr"/>
       <c r="L702" t="n">
-        <v>0.0022</v>
+        <v>0.0015</v>
       </c>
       <c r="M702" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(21,'20260623',9.506,9.506,9.469,9.519,9.465,NULL,0.0022,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(21,'20260623',9.5,9.5,9.469,9.519,9.465,NULL,0.0015,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -40469,10 +40469,10 @@
         </is>
       </c>
       <c r="F773" t="n">
-        <v>74.14</v>
+        <v>74.13</v>
       </c>
       <c r="G773" t="n">
-        <v>74.14</v>
+        <v>74.13</v>
       </c>
       <c r="H773" t="n">
         <v>74.14</v>
@@ -40485,11 +40485,11 @@
       </c>
       <c r="K773" t="inlineStr"/>
       <c r="L773" t="n">
-        <v>-0.0321</v>
+        <v>-0.0322</v>
       </c>
       <c r="M773" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(23,'20260622',74.14,74.14,74.14,74.45,74.04,NULL,-0.0321,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(23,'20260622',74.13,74.13,74.14,74.45,74.04,NULL,-0.0322,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -42318,10 +42318,10 @@
         </is>
       </c>
       <c r="F808" t="n">
-        <v>4201.8</v>
+        <v>4202.2</v>
       </c>
       <c r="G808" t="n">
-        <v>4201.8</v>
+        <v>4202.2</v>
       </c>
       <c r="H808" t="n">
         <v>4210.8</v>
@@ -42334,15 +42334,15 @@
       </c>
       <c r="K808" t="inlineStr">
         <is>
-          <t>3.25K</t>
+          <t>3.32K</t>
         </is>
       </c>
       <c r="L808" t="n">
-        <v>-0.0053</v>
+        <v>-0.0052</v>
       </c>
       <c r="M808" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(24,'20260622',4201.8,4201.8,4210.8,4213.6,4196.0,'3.25K',-0.0053,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(24,'20260622',4202.2,4202.2,4210.8,4213.6,4196.0,'3.32K',-0.0052,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -44118,10 +44118,10 @@
         </is>
       </c>
       <c r="F842" t="n">
-        <v>71798.10000000001</v>
+        <v>72000.35000000001</v>
       </c>
       <c r="G842" t="n">
-        <v>71798.10000000001</v>
+        <v>72000.35000000001</v>
       </c>
       <c r="H842" t="n">
         <v>72404.37</v>
@@ -44130,15 +44130,15 @@
         <v>72618.44</v>
       </c>
       <c r="J842" t="n">
-        <v>71798.10000000001</v>
+        <v>71789.13</v>
       </c>
       <c r="K842" t="inlineStr"/>
       <c r="L842" t="n">
-        <v>0.0077</v>
+        <v>0.0105</v>
       </c>
       <c r="M842" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(25,'20260623',71798.1,71798.1,72404.37,72618.44,71798.1,NULL,0.0077,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(25,'20260623',72000.35,72000.35,72404.37,72618.44,71789.13,NULL,0.0105,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -47700,11 +47700,11 @@
       </c>
       <c r="K912" t="inlineStr"/>
       <c r="L912" t="n">
-        <v>0.0017</v>
+        <v>0.0018</v>
       </c>
       <c r="M912" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(27,'20260622',101.03,101.03,101.0,101.04,101.01,NULL,0.0017,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(27,'20260622',101.03,101.03,101.0,101.04,101.01,NULL,0.0018,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -49397,10 +49397,10 @@
         </is>
       </c>
       <c r="F947" t="n">
-        <v>6.3395</v>
+        <v>6.344</v>
       </c>
       <c r="G947" t="n">
-        <v>6.3395</v>
+        <v>6.344</v>
       </c>
       <c r="H947" t="n">
         <v>6.361</v>
@@ -49413,11 +49413,11 @@
       </c>
       <c r="K947" t="inlineStr"/>
       <c r="L947" t="n">
-        <v>-0.0055</v>
+        <v>-0.0048</v>
       </c>
       <c r="M947" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(28,'20260622',6.3395,6.3395,6.361,6.3645,6.335,NULL,-0.0055,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(28,'20260622',6.344,6.344,6.361,6.3645,6.335,NULL,-0.0048,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
@@ -52823,10 +52823,10 @@
         </is>
       </c>
       <c r="F1017" t="n">
-        <v>64.83</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="G1017" t="n">
-        <v>64.83</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="H1017" t="n">
         <v>65.20999999999999</v>
@@ -52839,11 +52839,11 @@
       </c>
       <c r="K1017" t="inlineStr"/>
       <c r="L1017" t="n">
-        <v>-0.0214</v>
+        <v>-0.0213</v>
       </c>
       <c r="M1017" t="inlineStr">
         <is>
-          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(30,'20260622',64.83,64.83,65.21,65.32,64.44,NULL,-0.0214,GETDATE(),NULL);</t>
+          <t>INSERT INTO MK_YFINANCE_DATA (MAST_ID, TD, CLOSE_PRC, ADJ_CLOSE_PRC, OPEN_PRC, HIGH_PRC, LOW_PRC, VOLUME, CHG_RT, REG_DT, REMARK) VALUES(30,'20260622',64.85,64.85,65.21,65.32,64.44,NULL,-0.0213,GETDATE(),NULL);</t>
         </is>
       </c>
     </row>
